--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:41</t>
+    <t xml:space="preserve">2026-09-09 23:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:40</t>
+    <t xml:space="preserve">2026-09-18 10:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:29</t>
+    <t xml:space="preserve">2026-09-23 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:01</t>
+    <t xml:space="preserve">2026-10-02 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Negrete</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:12</t>
+    <t xml:space="preserve">2026-10-04 09:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:45</t>
+    <t xml:space="preserve">2026-10-05 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
